--- a/fire_inspection_forms/012_fire_drill_checklist--fire_inspection_forms.xlsx
+++ b/fire_inspection_forms/012_fire_drill_checklist--fire_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1033,8 +1033,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_2.1,_'label':_'manager',_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 2.1, 'label': 'Manager', 'value': 'manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2.2,_'label':_'hr',_'value':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2.2, 'label': 'HR', 'value': 'hr'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_2.3,_'label':_'fire_marshal',_'value':_'fire_marshal'}</t>
+          <t>fire_marshal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 2.3, 'label': 'Fire Marshal', 'value': 'fire_marshal'}</t>
+          <t>Fire Marshal</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4.1,_'label':_'fire_marshal',_'value':_'fire_marshal'}</t>
+          <t>fire_marshal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4.1, 'label': 'Fire Marshal', 'value': 'fire_marshal'}</t>
+          <t>Fire Marshal</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_4.2,_'label':_'fire_chief',_'value':_'fire_chief'}</t>
+          <t>fire_chief</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 4.2, 'label': 'Fire Chief', 'value': 'fire_chief'}</t>
+          <t>Fire Chief</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4.3,_'label':_'fire_captain',_'value':_'fire_captain'}</t>
+          <t>fire_captain</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4.3, 'label': 'Fire Captain', 'value': 'fire_captain'}</t>
+          <t>Fire Captain</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_5.1,_'label':_'fire_marshal',_'value':_'fire_marshal'}</t>
+          <t>fire_marshal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 5.1, 'label': 'Fire Marshal', 'value': 'fire_marshal'}</t>
+          <t>Fire Marshal</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5.2,_'label':_'fire_chief',_'value':_'fire_chief'}</t>
+          <t>fire_chief</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5.2, 'label': 'Fire Chief', 'value': 'fire_chief'}</t>
+          <t>Fire Chief</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5.3,_'label':_'fire_captain',_'value':_'fire_captain'}</t>
+          <t>fire_captain</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5.3, 'label': 'Fire Captain', 'value': 'fire_captain'}</t>
+          <t>Fire Captain</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_6.1,_'label':_'trained',_'value':_'trained'}</t>
+          <t>trained</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 6.1, 'label': 'Trained', 'value': 'trained'}</t>
+          <t>Trained</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_6.2,_'label':_'needs_refresher_training',_'value':_'needs_refresher_training'}</t>
+          <t>needs_refresher_training</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 6.2, 'label': 'Needs Refresher Training', 'value': 'needs_refresher_training'}</t>
+          <t>Needs Refresher Training</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_6.3,_'label':_'untrained',_'value':_'untrained'}</t>
+          <t>untrained</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 6.3, 'label': 'Untrained', 'value': 'untrained'}</t>
+          <t>Untrained</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_7.1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 7.1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_7.2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 7.2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_8.1,_'label':_'fire_extinguisher_a',_'value':_'fire_extinguisher_a'}</t>
+          <t>fire_extinguisher_a</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 8.1, 'label': 'Fire Extinguisher A', 'value': 'fire_extinguisher_a'}</t>
+          <t>Fire Extinguisher A</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_8.2,_'label':_'fire_extinguisher_b',_'value':_'fire_extinguisher_b'}</t>
+          <t>fire_extinguisher_b</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 8.2, 'label': 'Fire Extinguisher B', 'value': 'fire_extinguisher_b'}</t>
+          <t>Fire Extinguisher B</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_8.3,_'label':_'fire_extinguisher_c',_'value':_'fire_extinguisher_c'}</t>
+          <t>fire_extinguisher_c</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 8.3, 'label': 'Fire Extinguisher C', 'value': 'fire_extinguisher_c'}</t>
+          <t>Fire Extinguisher C</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_11.1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 11.1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_11.2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 11.2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_12.1,_'label':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 12.1, 'label': 'Monthly', 'value': 'monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_12.2,_'label':_'quarterly',_'value':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 12.2, 'label': 'Quarterly', 'value': 'quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_12.3,_'label':_'annually',_'value':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 12.3, 'label': 'Annually', 'value': 'annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_13.1,_'label':_'roll_call',_'value':_'roll_call'}</t>
+          <t>roll_call</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 13.1, 'label': 'Roll Call', 'value': 'roll_call'}</t>
+          <t>Roll Call</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_13.2,_'label':_'written_test',_'value':_'written_test'}</t>
+          <t>written_test</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 13.2, 'label': 'Written Test', 'value': 'written_test'}</t>
+          <t>Written Test</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_13.3,_'label':_'simulation',_'value':_'simulation'}</t>
+          <t>simulation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 13.3, 'label': 'Simulation', 'value': 'simulation'}</t>
+          <t>Simulation</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_14.1,_'label':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 14.1, 'label': 'Monthly', 'value': 'monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_14.2,_'label':_'quarterly',_'value':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 14.2, 'label': 'Quarterly', 'value': 'quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_14.3,_'label':_'annually',_'value':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 14.3, 'label': 'Annually', 'value': 'annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_15.1,_'label':_'every_1_year',_'value':_'every_1_year'}</t>
+          <t>every_1_year</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 15.1, 'label': 'Every 1 year', 'value': 'every_1_year'}</t>
+          <t>Every 1 year</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_15.2,_'label':_'every_2_years',_'value':_'every_2_years'}</t>
+          <t>every_2_years</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 15.2, 'label': 'Every 2 years', 'value': 'every_2_years'}</t>
+          <t>Every 2 years</t>
         </is>
       </c>
     </row>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_15.3,_'label':_'never',_'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 15.3, 'label': 'Never', 'value': 'never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_16.1,_'label':_'passed',_'value':_'passed'}</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 16.1, 'label': 'Passed', 'value': 'passed'}</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1606,12 +1606,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_16.2,_'label':_'failed',_'value':_'failed'}</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 16.2, 'label': 'Failed', 'value': 'failed'}</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_16.2,_'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 16.2, 'label': 'In Progress', 'value': 'in_progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_17.1,_'label':_'pass',_'value':_'pass'}</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 17.1, 'label': 'Pass', 'value': 'pass'}</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_17.2,_'label':_'fail',_'value':_'fail'}</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 17.2, 'label': 'Fail', 'value': 'fail'}</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_17.3,_'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 17.3, 'label': 'In Progress', 'value': 'in_progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1691,12 +1691,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_18.1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 18.1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1708,12 +1708,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_18.2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 18.2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1725,12 +1725,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_19.1,_'label':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 19.1, 'label': 'Completed', 'value': 'completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_19.2,_'label':_'partially_completed',_'value':_'partially_completed'}</t>
+          <t>partially_completed</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 19.2, 'label': 'Partially Completed', 'value': 'partially_completed'}</t>
+          <t>Partially Completed</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_19.3,_'label':_'not_completed',_'value':_'not_completed'}</t>
+          <t>not_completed</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 19.3, 'label': 'Not Completed', 'value': 'not_completed'}</t>
+          <t>Not Completed</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_20.1,_'label':_'fire_marshal',_'value':_'fire_marshal'}</t>
+          <t>fire_marshal</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 20.1, 'label': 'Fire Marshal', 'value': 'fire_marshal'}</t>
+          <t>Fire Marshal</t>
         </is>
       </c>
     </row>
@@ -1793,12 +1793,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_20.2,_'label':_'fire_chief',_'value':_'fire_chief'}</t>
+          <t>fire_chief</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 20.2, 'label': 'Fire Chief', 'value': 'fire_chief'}</t>
+          <t>Fire Chief</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_20.3,_'label':_'fire_captain',_'value':_'fire_captain'}</t>
+          <t>fire_captain</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 20.3, 'label': 'Fire Captain', 'value': 'fire_captain'}</t>
+          <t>Fire Captain</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_21.1,_'label':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 21.1, 'label': 'Completed', 'value': 'completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_21.2,_'label':_'not_completed',_'value':_'not_completed'}</t>
+          <t>not_completed</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 21.2, 'label': 'Not Completed', 'value': 'not_completed'}</t>
+          <t>Not Completed</t>
         </is>
       </c>
     </row>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_22.1,_'label':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 22.1, 'label': 'Monthly', 'value': 'monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_22.2,_'label':_'quarterly',_'value':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 22.2, 'label': 'Quarterly', 'value': 'quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1895,12 +1895,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_22.3,_'label':_'annually',_'value':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 22.3, 'label': 'Annually', 'value': 'annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
